--- a/message20260119.xlsx
+++ b/message20260119.xlsx
@@ -3913,7 +3913,7 @@
         <v>2</v>
       </c>
       <c r="O10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P10">
         <v>2</v>
@@ -3960,7 +3960,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P11">
         <v>2</v>
@@ -4007,7 +4007,7 @@
         <v>6</v>
       </c>
       <c r="O12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P12">
         <v>2</v>
@@ -4054,7 +4054,7 @@
         <v>7</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P13">
         <v>2</v>
@@ -4101,7 +4101,7 @@
         <v>8</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P14">
         <v>2</v>
@@ -4148,7 +4148,7 @@
         <v>185</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P15">
         <v>2</v>
@@ -7626,7 +7626,7 @@
         <v>408</v>
       </c>
       <c r="O89">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P89">
         <v>3</v>
@@ -7673,7 +7673,7 @@
         <v>409</v>
       </c>
       <c r="O90">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P90">
         <v>2</v>
@@ -7720,7 +7720,7 @@
         <v>410</v>
       </c>
       <c r="O91">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P91">
         <v>3</v>
@@ -7767,7 +7767,7 @@
         <v>411</v>
       </c>
       <c r="O92">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P92">
         <v>2</v>
@@ -7814,7 +7814,7 @@
         <v>412</v>
       </c>
       <c r="O93">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P93">
         <v>2</v>
@@ -7861,7 +7861,7 @@
         <v>413</v>
       </c>
       <c r="O94">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P94">
         <v>2</v>
@@ -7908,7 +7908,7 @@
         <v>447</v>
       </c>
       <c r="O95">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P95">
         <v>3</v>
@@ -7955,7 +7955,7 @@
         <v>449</v>
       </c>
       <c r="O96">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P96">
         <v>2</v>
@@ -8002,7 +8002,7 @@
         <v>450</v>
       </c>
       <c r="O97">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P97">
         <v>2</v>
@@ -8049,7 +8049,7 @@
         <v>453</v>
       </c>
       <c r="O98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P98">
         <v>3</v>
@@ -8096,7 +8096,7 @@
         <v>454</v>
       </c>
       <c r="O99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P99">
         <v>2</v>
@@ -8143,7 +8143,7 @@
         <v>457</v>
       </c>
       <c r="O100">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P100">
         <v>3</v>
@@ -8193,7 +8193,7 @@
         <v>2</v>
       </c>
       <c r="P101">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -8334,7 +8334,7 @@
         <v>2</v>
       </c>
       <c r="P104">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -8616,7 +8616,7 @@
         <v>2</v>
       </c>
       <c r="P110">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -8663,7 +8663,7 @@
         <v>2</v>
       </c>
       <c r="P111">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -8945,7 +8945,7 @@
         <v>2</v>
       </c>
       <c r="P117">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -9133,7 +9133,7 @@
         <v>2</v>
       </c>
       <c r="P121">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -9177,7 +9177,7 @@
         <v>529</v>
       </c>
       <c r="O122">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P122">
         <v>2</v>
@@ -9224,7 +9224,7 @@
         <v>530</v>
       </c>
       <c r="O123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P123">
         <v>2</v>
@@ -15099,7 +15099,7 @@
         <v>67</v>
       </c>
       <c r="O248">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P248">
         <v>4</v>
@@ -15146,7 +15146,7 @@
         <v>70</v>
       </c>
       <c r="O249">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P249">
         <v>2</v>
@@ -15193,7 +15193,7 @@
         <v>72</v>
       </c>
       <c r="O250">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P250">
         <v>4</v>
@@ -15240,7 +15240,7 @@
         <v>73</v>
       </c>
       <c r="O251">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P251">
         <v>2</v>
@@ -15287,7 +15287,7 @@
         <v>74</v>
       </c>
       <c r="O252">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P252">
         <v>2</v>
@@ -15334,7 +15334,7 @@
         <v>76</v>
       </c>
       <c r="O253">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P253">
         <v>2</v>
@@ -15381,7 +15381,7 @@
         <v>77</v>
       </c>
       <c r="O254">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P254">
         <v>2</v>
@@ -15428,7 +15428,7 @@
         <v>69</v>
       </c>
       <c r="O255">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P255">
         <v>3</v>
@@ -15475,7 +15475,7 @@
         <v>75</v>
       </c>
       <c r="O256">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P256">
         <v>2</v>
@@ -15522,7 +15522,7 @@
         <v>80</v>
       </c>
       <c r="O257">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P257">
         <v>2</v>
@@ -15569,7 +15569,7 @@
         <v>81</v>
       </c>
       <c r="O258">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P258">
         <v>3</v>
@@ -15616,7 +15616,7 @@
         <v>82</v>
       </c>
       <c r="O259">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P259">
         <v>2</v>
@@ -15663,7 +15663,7 @@
         <v>84</v>
       </c>
       <c r="O260">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P260">
         <v>3</v>
@@ -15710,7 +15710,7 @@
         <v>85</v>
       </c>
       <c r="O261">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P261">
         <v>3</v>
@@ -19423,10 +19423,10 @@
         <v>387</v>
       </c>
       <c r="O340">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P340">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19470,7 +19470,7 @@
         <v>398</v>
       </c>
       <c r="O341">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P341">
         <v>2</v>
@@ -19517,10 +19517,10 @@
         <v>403</v>
       </c>
       <c r="O342">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P342">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19564,7 +19564,7 @@
         <v>407</v>
       </c>
       <c r="O343">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P343">
         <v>2</v>
@@ -19611,7 +19611,7 @@
         <v>484</v>
       </c>
       <c r="O344">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P344">
         <v>2</v>
@@ -19658,7 +19658,7 @@
         <v>486</v>
       </c>
       <c r="O345">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P345">
         <v>2</v>
@@ -19705,7 +19705,7 @@
         <v>489</v>
       </c>
       <c r="O346">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P346">
         <v>2</v>
@@ -19752,7 +19752,7 @@
         <v>491</v>
       </c>
       <c r="O347">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P347">
         <v>2</v>
@@ -19799,7 +19799,7 @@
         <v>492</v>
       </c>
       <c r="O348">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P348">
         <v>2</v>
@@ -19846,7 +19846,7 @@
         <v>493</v>
       </c>
       <c r="O349">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P349">
         <v>2</v>
@@ -20222,7 +20222,7 @@
         <v>581</v>
       </c>
       <c r="O357">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P357">
         <v>3</v>
@@ -20269,7 +20269,7 @@
         <v>583</v>
       </c>
       <c r="O358">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P358">
         <v>2</v>
@@ -20316,7 +20316,7 @@
         <v>584</v>
       </c>
       <c r="O359">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P359">
         <v>2</v>
@@ -20363,7 +20363,7 @@
         <v>586</v>
       </c>
       <c r="O360">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P360">
         <v>3</v>
@@ -20410,7 +20410,7 @@
         <v>588</v>
       </c>
       <c r="O361">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P361">
         <v>2</v>
@@ -20457,7 +20457,7 @@
         <v>591</v>
       </c>
       <c r="O362">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P362">
         <v>2</v>
@@ -21447,7 +21447,7 @@
         <v>3</v>
       </c>
       <c r="P383">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21494,7 +21494,7 @@
         <v>3</v>
       </c>
       <c r="P384">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21588,7 +21588,7 @@
         <v>3</v>
       </c>
       <c r="P386">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21729,7 +21729,7 @@
         <v>3</v>
       </c>
       <c r="P389">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -22340,7 +22340,7 @@
         <v>2</v>
       </c>
       <c r="P402">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22387,7 +22387,7 @@
         <v>2</v>
       </c>
       <c r="P403">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22434,7 +22434,7 @@
         <v>2</v>
       </c>
       <c r="P404">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22575,7 +22575,7 @@
         <v>2</v>
       </c>
       <c r="P407">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22622,7 +22622,7 @@
         <v>2</v>
       </c>
       <c r="P408">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22763,7 +22763,7 @@
         <v>2</v>
       </c>
       <c r="P411">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22904,7 +22904,7 @@
         <v>2</v>
       </c>
       <c r="P414">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22951,7 +22951,7 @@
         <v>2</v>
       </c>
       <c r="P415">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23186,7 +23186,7 @@
         <v>2</v>
       </c>
       <c r="P420">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23280,7 +23280,7 @@
         <v>2</v>
       </c>
       <c r="P422">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23374,7 +23374,7 @@
         <v>2</v>
       </c>
       <c r="P424">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23421,7 +23421,7 @@
         <v>2</v>
       </c>
       <c r="P425">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23515,7 +23515,7 @@
         <v>2</v>
       </c>
       <c r="P427">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23562,7 +23562,7 @@
         <v>2</v>
       </c>
       <c r="P428">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -24310,7 +24310,7 @@
         <v>817</v>
       </c>
       <c r="O445">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P445">
         <v>3</v>
@@ -24357,7 +24357,7 @@
         <v>819</v>
       </c>
       <c r="O446">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P446">
         <v>3</v>
@@ -24404,7 +24404,7 @@
         <v>821</v>
       </c>
       <c r="O447">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P447">
         <v>2</v>
@@ -24451,7 +24451,7 @@
         <v>822</v>
       </c>
       <c r="O448">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P448">
         <v>2</v>
@@ -24498,7 +24498,7 @@
         <v>823</v>
       </c>
       <c r="O449">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P449">
         <v>3</v>
@@ -24545,7 +24545,7 @@
         <v>824</v>
       </c>
       <c r="O450">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P450">
         <v>2</v>
@@ -25015,7 +25015,7 @@
         <v>12</v>
       </c>
       <c r="O460">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P460">
         <v>6</v>
@@ -25065,7 +25065,7 @@
         <v>1</v>
       </c>
       <c r="P461">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25253,7 +25253,7 @@
         <v>1</v>
       </c>
       <c r="P465">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25441,7 +25441,7 @@
         <v>1</v>
       </c>
       <c r="P469">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25629,7 +25629,7 @@
         <v>1</v>
       </c>
       <c r="P473">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25676,7 +25676,7 @@
         <v>1</v>
       </c>
       <c r="P474">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25911,7 +25911,7 @@
         <v>1</v>
       </c>
       <c r="P479">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26005,7 +26005,7 @@
         <v>1</v>
       </c>
       <c r="P481">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26099,7 +26099,7 @@
         <v>1</v>
       </c>
       <c r="P483">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26146,7 +26146,7 @@
         <v>1</v>
       </c>
       <c r="P484">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26240,7 +26240,7 @@
         <v>1</v>
       </c>
       <c r="P486">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26381,7 +26381,7 @@
         <v>1</v>
       </c>
       <c r="P489">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26522,7 +26522,7 @@
         <v>1</v>
       </c>
       <c r="P492">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26613,7 +26613,7 @@
         <v>17</v>
       </c>
       <c r="O494">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P494">
         <v>6</v>
@@ -26660,7 +26660,7 @@
         <v>19</v>
       </c>
       <c r="O495">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P495">
         <v>3</v>
@@ -26707,7 +26707,7 @@
         <v>20</v>
       </c>
       <c r="O496">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P496">
         <v>2</v>
@@ -26754,7 +26754,7 @@
         <v>24</v>
       </c>
       <c r="O497">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P497">
         <v>6</v>
@@ -26801,7 +26801,7 @@
         <v>26</v>
       </c>
       <c r="O498">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P498">
         <v>3</v>
@@ -26848,7 +26848,7 @@
         <v>36</v>
       </c>
       <c r="O499">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P499">
         <v>6</v>
@@ -26895,7 +26895,7 @@
         <v>37</v>
       </c>
       <c r="O500">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P500">
         <v>3</v>
@@ -26942,7 +26942,7 @@
         <v>38</v>
       </c>
       <c r="O501">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P501">
         <v>2</v>
@@ -26989,7 +26989,7 @@
         <v>42</v>
       </c>
       <c r="O502">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P502">
         <v>2</v>
@@ -27036,7 +27036,7 @@
         <v>45</v>
       </c>
       <c r="O503">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P503">
         <v>3</v>
@@ -27083,7 +27083,7 @@
         <v>47</v>
       </c>
       <c r="O504">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P504">
         <v>6</v>
@@ -27130,7 +27130,7 @@
         <v>49</v>
       </c>
       <c r="O505">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P505">
         <v>6</v>
@@ -27177,7 +27177,7 @@
         <v>50</v>
       </c>
       <c r="O506">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P506">
         <v>2</v>
@@ -27224,7 +27224,7 @@
         <v>51</v>
       </c>
       <c r="O507">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P507">
         <v>3</v>
@@ -27271,7 +27271,7 @@
         <v>53</v>
       </c>
       <c r="O508">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P508">
         <v>2</v>
@@ -27318,7 +27318,7 @@
         <v>54</v>
       </c>
       <c r="O509">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P509">
         <v>6</v>
@@ -27365,7 +27365,7 @@
         <v>57</v>
       </c>
       <c r="O510">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P510">
         <v>3</v>
@@ -27412,7 +27412,7 @@
         <v>59</v>
       </c>
       <c r="O511">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P511">
         <v>2</v>
@@ -27459,7 +27459,7 @@
         <v>62</v>
       </c>
       <c r="O512">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P512">
         <v>3</v>
@@ -27506,7 +27506,7 @@
         <v>316</v>
       </c>
       <c r="O513">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P513">
         <v>3</v>
@@ -27553,7 +27553,7 @@
         <v>317</v>
       </c>
       <c r="O514">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P514">
         <v>2</v>
@@ -27600,7 +27600,7 @@
         <v>318</v>
       </c>
       <c r="O515">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P515">
         <v>2</v>
@@ -27647,7 +27647,7 @@
         <v>319</v>
       </c>
       <c r="O516">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P516">
         <v>3</v>
@@ -27694,7 +27694,7 @@
         <v>320</v>
       </c>
       <c r="O517">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P517">
         <v>2</v>
@@ -27741,7 +27741,7 @@
         <v>321</v>
       </c>
       <c r="O518">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P518">
         <v>3</v>
@@ -27788,7 +27788,7 @@
         <v>322</v>
       </c>
       <c r="O519">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P519">
         <v>3</v>
@@ -27835,7 +27835,7 @@
         <v>323</v>
       </c>
       <c r="O520">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P520">
         <v>2</v>
@@ -27882,7 +27882,7 @@
         <v>324</v>
       </c>
       <c r="O521">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P521">
         <v>2</v>
@@ -27929,7 +27929,7 @@
         <v>325</v>
       </c>
       <c r="O522">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P522">
         <v>3</v>
@@ -27976,7 +27976,7 @@
         <v>326</v>
       </c>
       <c r="O523">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P523">
         <v>2</v>
@@ -28023,7 +28023,7 @@
         <v>327</v>
       </c>
       <c r="O524">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P524">
         <v>3</v>
@@ -28070,7 +28070,7 @@
         <v>328</v>
       </c>
       <c r="O525">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P525">
         <v>2</v>
@@ -28117,7 +28117,7 @@
         <v>329</v>
       </c>
       <c r="O526">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P526">
         <v>2</v>
@@ -28164,10 +28164,10 @@
         <v>281</v>
       </c>
       <c r="O527">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P527">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28211,7 +28211,7 @@
         <v>282</v>
       </c>
       <c r="O528">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P528">
         <v>6</v>
@@ -28258,7 +28258,7 @@
         <v>285</v>
       </c>
       <c r="O529">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P529">
         <v>4</v>
@@ -28305,10 +28305,10 @@
         <v>288</v>
       </c>
       <c r="O530">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P530">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28352,7 +28352,7 @@
         <v>292</v>
       </c>
       <c r="O531">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P531">
         <v>6</v>
@@ -28399,7 +28399,7 @@
         <v>295</v>
       </c>
       <c r="O532">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P532">
         <v>4</v>
@@ -28446,10 +28446,10 @@
         <v>297</v>
       </c>
       <c r="O533">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P533">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28493,10 +28493,10 @@
         <v>302</v>
       </c>
       <c r="O534">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P534">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28540,7 +28540,7 @@
         <v>303</v>
       </c>
       <c r="O535">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P535">
         <v>4</v>
@@ -28587,7 +28587,7 @@
         <v>305</v>
       </c>
       <c r="O536">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P536">
         <v>4</v>
@@ -28634,7 +28634,7 @@
         <v>306</v>
       </c>
       <c r="O537">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P537">
         <v>4</v>
@@ -28681,10 +28681,10 @@
         <v>309</v>
       </c>
       <c r="O538">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P538">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28728,7 +28728,7 @@
         <v>312</v>
       </c>
       <c r="O539">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P539">
         <v>6</v>
@@ -28775,10 +28775,10 @@
         <v>313</v>
       </c>
       <c r="O540">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P540">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28822,7 +28822,7 @@
         <v>314</v>
       </c>
       <c r="O541">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P541">
         <v>4</v>
@@ -28869,10 +28869,10 @@
         <v>315</v>
       </c>
       <c r="O542">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P542">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29292,7 +29292,7 @@
         <v>287</v>
       </c>
       <c r="O551">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P551">
         <v>3</v>
@@ -29339,7 +29339,7 @@
         <v>289</v>
       </c>
       <c r="O552">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P552">
         <v>2</v>
@@ -29386,7 +29386,7 @@
         <v>291</v>
       </c>
       <c r="O553">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P553">
         <v>3</v>
@@ -29433,7 +29433,7 @@
         <v>294</v>
       </c>
       <c r="O554">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P554">
         <v>3</v>
@@ -29480,7 +29480,7 @@
         <v>298</v>
       </c>
       <c r="O555">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P555">
         <v>3</v>
@@ -29527,7 +29527,7 @@
         <v>300</v>
       </c>
       <c r="O556">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P556">
         <v>2</v>
@@ -29574,7 +29574,7 @@
         <v>301</v>
       </c>
       <c r="O557">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P557">
         <v>3</v>
@@ -29621,7 +29621,7 @@
         <v>304</v>
       </c>
       <c r="O558">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P558">
         <v>3</v>
@@ -29668,7 +29668,7 @@
         <v>307</v>
       </c>
       <c r="O559">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P559">
         <v>2</v>
@@ -29715,7 +29715,7 @@
         <v>311</v>
       </c>
       <c r="O560">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P560">
         <v>3</v>
@@ -29762,7 +29762,7 @@
         <v>308</v>
       </c>
       <c r="O561">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P561">
         <v>1</v>
@@ -29809,7 +29809,7 @@
         <v>310</v>
       </c>
       <c r="O562">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P562">
         <v>1</v>
@@ -30373,7 +30373,7 @@
         <v>417</v>
       </c>
       <c r="O574">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P574">
         <v>1</v>
@@ -30420,7 +30420,7 @@
         <v>419</v>
       </c>
       <c r="O575">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P575">
         <v>3</v>
@@ -30467,7 +30467,7 @@
         <v>420</v>
       </c>
       <c r="O576">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P576">
         <v>1</v>
@@ -31783,7 +31783,7 @@
         <v>572</v>
       </c>
       <c r="O604">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P604">
         <v>4</v>
@@ -31830,7 +31830,7 @@
         <v>573</v>
       </c>
       <c r="O605">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P605">
         <v>4</v>
@@ -31877,7 +31877,7 @@
         <v>574</v>
       </c>
       <c r="O606">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P606">
         <v>2</v>
@@ -31924,7 +31924,7 @@
         <v>575</v>
       </c>
       <c r="O607">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P607">
         <v>4</v>
@@ -31971,7 +31971,7 @@
         <v>576</v>
       </c>
       <c r="O608">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P608">
         <v>4</v>
@@ -32018,7 +32018,7 @@
         <v>577</v>
       </c>
       <c r="O609">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P609">
         <v>3</v>
@@ -32065,7 +32065,7 @@
         <v>578</v>
       </c>
       <c r="O610">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P610">
         <v>2</v>
@@ -32112,7 +32112,7 @@
         <v>579</v>
       </c>
       <c r="O611">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P611">
         <v>4</v>
@@ -32159,7 +32159,7 @@
         <v>580</v>
       </c>
       <c r="O612">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P612">
         <v>2</v>
@@ -32394,7 +32394,7 @@
         <v>644</v>
       </c>
       <c r="O617">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P617">
         <v>6</v>
@@ -32441,10 +32441,10 @@
         <v>645</v>
       </c>
       <c r="O618">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P618">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32488,7 +32488,7 @@
         <v>646</v>
       </c>
       <c r="O619">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P619">
         <v>6</v>
@@ -32535,7 +32535,7 @@
         <v>671</v>
       </c>
       <c r="O620">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P620">
         <v>3</v>
@@ -32582,7 +32582,7 @@
         <v>672</v>
       </c>
       <c r="O621">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P621">
         <v>2</v>
@@ -32629,7 +32629,7 @@
         <v>673</v>
       </c>
       <c r="O622">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P622">
         <v>3</v>
@@ -32676,7 +32676,7 @@
         <v>674</v>
       </c>
       <c r="O623">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P623">
         <v>2</v>
@@ -32723,7 +32723,7 @@
         <v>675</v>
       </c>
       <c r="O624">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P624">
         <v>2</v>
@@ -33804,7 +33804,7 @@
         <v>810</v>
       </c>
       <c r="O647">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P647">
         <v>3</v>
@@ -33851,7 +33851,7 @@
         <v>811</v>
       </c>
       <c r="O648">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P648">
         <v>6</v>
@@ -33898,7 +33898,7 @@
         <v>812</v>
       </c>
       <c r="O649">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P649">
         <v>3</v>
@@ -33945,7 +33945,7 @@
         <v>813</v>
       </c>
       <c r="O650">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P650">
         <v>3</v>
@@ -33992,7 +33992,7 @@
         <v>814</v>
       </c>
       <c r="O651">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P651">
         <v>2</v>
@@ -34039,7 +34039,7 @@
         <v>815</v>
       </c>
       <c r="O652">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P652">
         <v>6</v>
@@ -34086,7 +34086,7 @@
         <v>163</v>
       </c>
       <c r="O653">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P653">
         <v>3</v>
@@ -34133,7 +34133,7 @@
         <v>164</v>
       </c>
       <c r="O654">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P654">
         <v>2</v>
@@ -34180,7 +34180,7 @@
         <v>165</v>
       </c>
       <c r="O655">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P655">
         <v>3</v>
@@ -34227,7 +34227,7 @@
         <v>168</v>
       </c>
       <c r="O656">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P656">
         <v>3</v>
@@ -34274,7 +34274,7 @@
         <v>170</v>
       </c>
       <c r="O657">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P657">
         <v>3</v>
@@ -34321,7 +34321,7 @@
         <v>171</v>
       </c>
       <c r="O658">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P658">
         <v>3</v>
@@ -34368,7 +34368,7 @@
         <v>172</v>
       </c>
       <c r="O659">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P659">
         <v>2</v>
@@ -34415,7 +34415,7 @@
         <v>173</v>
       </c>
       <c r="O660">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P660">
         <v>3</v>
@@ -34462,7 +34462,7 @@
         <v>174</v>
       </c>
       <c r="O661">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P661">
         <v>3</v>
@@ -34509,7 +34509,7 @@
         <v>175</v>
       </c>
       <c r="O662">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P662">
         <v>3</v>
@@ -34556,7 +34556,7 @@
         <v>176</v>
       </c>
       <c r="O663">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P663">
         <v>2</v>
@@ -34603,7 +34603,7 @@
         <v>177</v>
       </c>
       <c r="O664">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P664">
         <v>3</v>
@@ -34650,7 +34650,7 @@
         <v>178</v>
       </c>
       <c r="O665">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P665">
         <v>3</v>
@@ -34697,7 +34697,7 @@
         <v>179</v>
       </c>
       <c r="O666">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P666">
         <v>3</v>
@@ -34932,7 +34932,7 @@
         <v>108</v>
       </c>
       <c r="O671">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P671">
         <v>2</v>
@@ -34979,7 +34979,7 @@
         <v>112</v>
       </c>
       <c r="O672">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P672">
         <v>2</v>
@@ -35026,7 +35026,7 @@
         <v>123</v>
       </c>
       <c r="O673">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P673">
         <v>2</v>
@@ -35073,7 +35073,7 @@
         <v>126</v>
       </c>
       <c r="O674">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P674">
         <v>2</v>
@@ -35120,7 +35120,7 @@
         <v>133</v>
       </c>
       <c r="O675">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P675">
         <v>2</v>
@@ -35167,7 +35167,7 @@
         <v>134</v>
       </c>
       <c r="O676">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P676">
         <v>3</v>
@@ -35214,7 +35214,7 @@
         <v>140</v>
       </c>
       <c r="O677">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P677">
         <v>2</v>
@@ -35261,7 +35261,7 @@
         <v>143</v>
       </c>
       <c r="O678">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P678">
         <v>2</v>
@@ -35308,7 +35308,7 @@
         <v>144</v>
       </c>
       <c r="O679">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P679">
         <v>2</v>
@@ -35355,7 +35355,7 @@
         <v>145</v>
       </c>
       <c r="O680">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P680">
         <v>3</v>
@@ -35402,7 +35402,7 @@
         <v>158</v>
       </c>
       <c r="O681">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P681">
         <v>3</v>
@@ -35449,7 +35449,7 @@
         <v>159</v>
       </c>
       <c r="O682">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P682">
         <v>2</v>
@@ -35496,7 +35496,7 @@
         <v>160</v>
       </c>
       <c r="O683">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P683">
         <v>2</v>
@@ -35543,7 +35543,7 @@
         <v>162</v>
       </c>
       <c r="O684">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P684">
         <v>3</v>
@@ -35590,7 +35590,7 @@
         <v>125</v>
       </c>
       <c r="O685">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P685">
         <v>2</v>
@@ -35637,7 +35637,7 @@
         <v>128</v>
       </c>
       <c r="O686">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P686">
         <v>2</v>
@@ -35684,7 +35684,7 @@
         <v>139</v>
       </c>
       <c r="O687">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P687">
         <v>2</v>
@@ -35731,7 +35731,7 @@
         <v>142</v>
       </c>
       <c r="O688">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P688">
         <v>2</v>
@@ -35778,7 +35778,7 @@
         <v>148</v>
       </c>
       <c r="O689">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P689">
         <v>2</v>
@@ -35825,7 +35825,7 @@
         <v>149</v>
       </c>
       <c r="O690">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P690">
         <v>2</v>
@@ -35872,7 +35872,7 @@
         <v>152</v>
       </c>
       <c r="O691">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P691">
         <v>2</v>
@@ -36624,7 +36624,7 @@
         <v>374</v>
       </c>
       <c r="O707">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P707">
         <v>3</v>
@@ -36671,7 +36671,7 @@
         <v>376</v>
       </c>
       <c r="O708">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P708">
         <v>2</v>
@@ -36718,7 +36718,7 @@
         <v>377</v>
       </c>
       <c r="O709">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P709">
         <v>2</v>
@@ -36765,7 +36765,7 @@
         <v>378</v>
       </c>
       <c r="O710">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P710">
         <v>3</v>
@@ -36812,7 +36812,7 @@
         <v>379</v>
       </c>
       <c r="O711">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P711">
         <v>2</v>
@@ -36859,7 +36859,7 @@
         <v>380</v>
       </c>
       <c r="O712">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P712">
         <v>3</v>
@@ -36906,7 +36906,7 @@
         <v>382</v>
       </c>
       <c r="O713">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P713">
         <v>3</v>
@@ -36953,7 +36953,7 @@
         <v>386</v>
       </c>
       <c r="O714">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P714">
         <v>2</v>
@@ -37000,7 +37000,7 @@
         <v>388</v>
       </c>
       <c r="O715">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P715">
         <v>2</v>
@@ -37047,7 +37047,7 @@
         <v>391</v>
       </c>
       <c r="O716">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P716">
         <v>2</v>
@@ -37094,7 +37094,7 @@
         <v>393</v>
       </c>
       <c r="O717">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P717">
         <v>1</v>
@@ -37141,7 +37141,7 @@
         <v>395</v>
       </c>
       <c r="O718">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P718">
         <v>3</v>
@@ -37846,7 +37846,7 @@
         <v>404</v>
       </c>
       <c r="O733">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P733">
         <v>3</v>
@@ -37893,7 +37893,7 @@
         <v>405</v>
       </c>
       <c r="O734">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P734">
         <v>2</v>
@@ -37940,7 +37940,7 @@
         <v>406</v>
       </c>
       <c r="O735">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P735">
         <v>3</v>
@@ -38084,7 +38084,7 @@
         <v>3</v>
       </c>
       <c r="P738">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38131,7 +38131,7 @@
         <v>3</v>
       </c>
       <c r="P739">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39585,7 +39585,7 @@
         <v>600</v>
       </c>
       <c r="O770">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P770">
         <v>1</v>
@@ -39632,7 +39632,7 @@
         <v>601</v>
       </c>
       <c r="O771">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P771">
         <v>1</v>
@@ -39679,7 +39679,7 @@
         <v>602</v>
       </c>
       <c r="O772">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P772">
         <v>6</v>
@@ -39726,7 +39726,7 @@
         <v>603</v>
       </c>
       <c r="O773">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P773">
         <v>2</v>
@@ -39773,7 +39773,7 @@
         <v>605</v>
       </c>
       <c r="O774">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P774">
         <v>2</v>
@@ -39820,7 +39820,7 @@
         <v>606</v>
       </c>
       <c r="O775">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P775">
         <v>1</v>
@@ -39867,7 +39867,7 @@
         <v>607</v>
       </c>
       <c r="O776">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P776">
         <v>1</v>
@@ -39914,7 +39914,7 @@
         <v>610</v>
       </c>
       <c r="O777">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P777">
         <v>6</v>
@@ -39961,7 +39961,7 @@
         <v>613</v>
       </c>
       <c r="O778">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P778">
         <v>6</v>
@@ -40008,7 +40008,7 @@
         <v>614</v>
       </c>
       <c r="O779">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P779">
         <v>2</v>
@@ -40055,7 +40055,7 @@
         <v>615</v>
       </c>
       <c r="O780">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P780">
         <v>6</v>
@@ -40619,7 +40619,7 @@
         <v>657</v>
       </c>
       <c r="O792">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P792">
         <v>2</v>
@@ -40666,7 +40666,7 @@
         <v>658</v>
       </c>
       <c r="O793">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P793">
         <v>2</v>
@@ -40713,7 +40713,7 @@
         <v>659</v>
       </c>
       <c r="O794">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P794">
         <v>3</v>
@@ -40760,7 +40760,7 @@
         <v>660</v>
       </c>
       <c r="O795">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P795">
         <v>6</v>
@@ -40807,7 +40807,7 @@
         <v>661</v>
       </c>
       <c r="O796">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P796">
         <v>2</v>
@@ -40854,7 +40854,7 @@
         <v>662</v>
       </c>
       <c r="O797">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P797">
         <v>3</v>
@@ -40901,7 +40901,7 @@
         <v>663</v>
       </c>
       <c r="O798">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P798">
         <v>6</v>
@@ -40948,7 +40948,7 @@
         <v>664</v>
       </c>
       <c r="O799">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P799">
         <v>2</v>
@@ -41841,7 +41841,7 @@
         <v>731</v>
       </c>
       <c r="O818">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P818">
         <v>1</v>
@@ -41888,7 +41888,7 @@
         <v>732</v>
       </c>
       <c r="O819">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P819">
         <v>2</v>
@@ -41935,7 +41935,7 @@
         <v>733</v>
       </c>
       <c r="O820">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P820">
         <v>1</v>
@@ -41982,7 +41982,7 @@
         <v>734</v>
       </c>
       <c r="O821">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P821">
         <v>1</v>
@@ -42029,7 +42029,7 @@
         <v>735</v>
       </c>
       <c r="O822">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P822">
         <v>1</v>
@@ -42076,7 +42076,7 @@
         <v>736</v>
       </c>
       <c r="O823">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P823">
         <v>1</v>
@@ -42123,7 +42123,7 @@
         <v>737</v>
       </c>
       <c r="O824">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P824">
         <v>2</v>
@@ -42170,7 +42170,7 @@
         <v>738</v>
       </c>
       <c r="O825">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P825">
         <v>1</v>
@@ -42217,7 +42217,7 @@
         <v>739</v>
       </c>
       <c r="O826">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P826">
         <v>1</v>
@@ -42264,7 +42264,7 @@
         <v>740</v>
       </c>
       <c r="O827">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P827">
         <v>1</v>
@@ -42311,7 +42311,7 @@
         <v>741</v>
       </c>
       <c r="O828">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P828">
         <v>1</v>
@@ -42358,7 +42358,7 @@
         <v>742</v>
       </c>
       <c r="O829">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P829">
         <v>1</v>
@@ -42405,7 +42405,7 @@
         <v>743</v>
       </c>
       <c r="O830">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P830">
         <v>1</v>
@@ -42452,7 +42452,7 @@
         <v>744</v>
       </c>
       <c r="O831">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P831">
         <v>1</v>
@@ -42499,7 +42499,7 @@
         <v>745</v>
       </c>
       <c r="O832">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P832">
         <v>1</v>
@@ -42546,7 +42546,7 @@
         <v>746</v>
       </c>
       <c r="O833">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P833">
         <v>1</v>
@@ -42593,7 +42593,7 @@
         <v>747</v>
       </c>
       <c r="O834">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P834">
         <v>1</v>
@@ -42640,7 +42640,7 @@
         <v>748</v>
       </c>
       <c r="O835">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P835">
         <v>2</v>
@@ -42687,7 +42687,7 @@
         <v>749</v>
       </c>
       <c r="O836">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P836">
         <v>1</v>
@@ -42734,7 +42734,7 @@
         <v>780</v>
       </c>
       <c r="O837">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P837">
         <v>3</v>
@@ -42781,7 +42781,7 @@
         <v>781</v>
       </c>
       <c r="O838">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P838">
         <v>2</v>
@@ -42828,7 +42828,7 @@
         <v>782</v>
       </c>
       <c r="O839">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P839">
         <v>3</v>
@@ -42875,7 +42875,7 @@
         <v>828</v>
       </c>
       <c r="O840">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P840">
         <v>3</v>
@@ -42922,7 +42922,7 @@
         <v>831</v>
       </c>
       <c r="O841">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P841">
         <v>2</v>
@@ -42969,7 +42969,7 @@
         <v>837</v>
       </c>
       <c r="O842">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P842">
         <v>2</v>
@@ -43016,7 +43016,7 @@
         <v>839</v>
       </c>
       <c r="O843">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P843">
         <v>6</v>
@@ -43063,7 +43063,7 @@
         <v>840</v>
       </c>
       <c r="O844">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P844">
         <v>3</v>
@@ -43110,7 +43110,7 @@
         <v>842</v>
       </c>
       <c r="O845">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P845">
         <v>6</v>
@@ -43157,7 +43157,7 @@
         <v>843</v>
       </c>
       <c r="O846">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P846">
         <v>2</v>
@@ -43204,7 +43204,7 @@
         <v>844</v>
       </c>
       <c r="O847">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P847">
         <v>3</v>
@@ -43251,7 +43251,7 @@
         <v>847</v>
       </c>
       <c r="O848">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P848">
         <v>3</v>
@@ -43298,7 +43298,7 @@
         <v>848</v>
       </c>
       <c r="O849">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P849">
         <v>2</v>
@@ -43345,7 +43345,7 @@
         <v>849</v>
       </c>
       <c r="O850">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P850">
         <v>2</v>
@@ -43392,7 +43392,7 @@
         <v>850</v>
       </c>
       <c r="O851">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P851">
         <v>3</v>
@@ -43439,7 +43439,7 @@
         <v>851</v>
       </c>
       <c r="O852">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P852">
         <v>3</v>
